--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-moped-ext-sonderklasse.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-moped-ext-sonderklasse.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>KLAS – Allgemeine Gebührenklasse/Sonderklasse</t>
+    <t>KLAS: Allgemeine Gebuehrenklasse bzw. Sonderklasse</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -248,9 +248,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"KLAS – Allgemeine Gebührenklasse/Sonderklasse" </t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -844,10 +841,10 @@
         <v>77</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -910,7 +907,7 @@
         <v>19</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>19</v>
@@ -918,10 +915,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,25 +929,25 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,30 +998,30 @@
         <v>19</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="AJ3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1047,13 +1044,13 @@
         <v>19</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>29</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1092,19 +1089,19 @@
         <v>19</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1116,7 +1113,7 @@
         <v>19</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>19</v>
@@ -1124,10 +1121,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1135,10 +1132,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>19</v>
@@ -1150,16 +1147,16 @@
         <v>19</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1209,13 +1206,13 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>19</v>
@@ -1224,15 +1221,15 @@
         <v>19</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1243,7 +1240,7 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>19</v>
@@ -1255,13 +1252,13 @@
         <v>19</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1288,11 +1285,11 @@
         <v>19</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>19</v>
@@ -1310,22 +1307,22 @@
         <v>19</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="AK6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
